--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32160" windowHeight="17020"/>
+    <workbookView windowHeight="16580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </si>
   <si>
     <t>Note:
-1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 100 pieces of data.
+1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 1000 pieces of data.
 2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).
 3.'Username', 'Name', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
 4.'Password' must contains at least six characters, uppercase and lowercase letters, digits.
@@ -46,8 +46,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -71,21 +71,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -101,24 +109,9 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -132,15 +125,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -153,9 +138,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,6 +162,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -177,16 +177,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -194,28 +216,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,175 +242,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,8 +427,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -437,6 +437,17 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -453,15 +464,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -483,11 +485,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -524,148 +524,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16580"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
   <si>
     <t>Username</t>
   </si>
@@ -31,6 +31,9 @@
     <t>Role</t>
   </si>
   <si>
+    <t>Expired Time</t>
+  </si>
+  <si>
     <t>Note:
 1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 1000 pieces of data.
 2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).
@@ -38,7 +41,8 @@
 4.'Password' must contains at least six characters, uppercase and lowercase letters, digits.
 5.'Username' must contains 2 to 20 characters and cannot be duplicated as the existing user.
 6.'Name' must contains 4 to 40 characters.
-7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.</t>
+7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
+8.'Expired Time' format should match yyyy-MM-dd HH:mm</t>
   </si>
 </sst>
 </file>
@@ -46,10 +50,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -77,6 +81,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -85,15 +103,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -107,108 +158,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,79 +240,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -320,97 +414,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -437,17 +441,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -485,9 +478,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -521,161 +516,177 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1003,35 +1014,38 @@
     <col min="3" max="3" width="20.6785714285714" customWidth="1"/>
     <col min="4" max="4" width="23.6964285714286" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="18.6428571428571" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="s">
+        <v>6</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8">
   <si>
     <t>Username</t>
   </si>
@@ -31,7 +31,10 @@
     <t>Role</t>
   </si>
   <si>
-    <t>Expired Time</t>
+    <t>Expired Date</t>
+  </si>
+  <si>
+    <t>Introduction</t>
   </si>
   <si>
     <t>Note:
@@ -42,7 +45,7 @@
 5.'Username' must contains 2 to 20 characters and cannot be duplicated as the existing user.
 6.'Name' must contains 4 to 40 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
-8.'Expired Time' format should match yyyy-MM-dd HH:mm</t>
+8.'Expired Time' format should match yyyy-MM-dd</t>
   </si>
 </sst>
 </file>
@@ -51,11 +54,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -74,8 +77,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color theme="1"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -88,18 +97,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -111,6 +113,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -118,9 +174,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -134,92 +227,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,6 +243,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -246,175 +393,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,20 +437,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -478,10 +484,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -502,21 +515,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -525,155 +523,166 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
@@ -684,6 +693,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1006,8 +1016,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="20.2410714285714" customWidth="1"/>
     <col min="2" max="2" width="21.5446428571429" customWidth="1"/>
@@ -1015,9 +1025,10 @@
     <col min="4" max="4" width="23.6964285714286" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="18.6428571428571" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.6428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1036,16 +1047,19 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowHeight="16960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Username</t>
   </si>
@@ -45,7 +45,8 @@
 5.'Username' must contains 2 to 20 characters and cannot be duplicated as the existing user.
 6.'Name' must contains 4 to 40 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
-8.'Expired Time' format should match yyyy-MM-dd</t>
+8.'Expired Time' format should match yyyy-MM-dd.
+9. 'Introduction' should less than 1000 character.</t>
   </si>
 </sst>
 </file>
@@ -53,10 +54,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -84,6 +85,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -97,9 +105,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,67 +130,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -189,36 +144,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -227,8 +152,84 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,13 +244,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,7 +406,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,157 +418,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,6 +453,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -463,6 +488,26 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -490,195 +535,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1014,7 +1015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16960"/>
+    <workbookView windowHeight="16600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 6.'Name' must contains 4 to 40 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
 8.'Expired Time' format should match yyyy-MM-dd.
-9. 'Introduction' should less than 1000 character.</t>
+9.'Introduction' should less than 1000 character.</t>
   </si>
 </sst>
 </file>
@@ -54,12 +54,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -68,33 +68,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="Arial Regular"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="方正书宋_GBK"/>
+      <name val="Arial Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
-      <name val="Helvetica"/>
+      <name val="Arial Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -107,14 +129,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -128,19 +142,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -152,84 +187,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -244,25 +250,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,157 +376,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,6 +441,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -454,6 +478,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -464,30 +503,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,190 +527,182 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1018,49 +1025,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.2410714285714" customWidth="1"/>
-    <col min="2" max="2" width="21.5446428571429" customWidth="1"/>
-    <col min="3" max="3" width="20.6785714285714" customWidth="1"/>
-    <col min="4" max="4" width="23.6964285714286" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.6428571428571" customWidth="1"/>
+    <col min="1" max="1" width="20.2410714285714" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5446428571429" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6785714285714" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.6964285714286" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.6428571428571" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="12.8" spans="1:7">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16600"/>
+    <workbookView windowHeight="15800"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,9 @@
 1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 1000 pieces of data.
 2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).
 3.'Username', 'Name', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
-4.'Password' must contains at least six characters, uppercase and lowercase letters, digits.
-5.'Username' must contains 2 to 20 characters and cannot be duplicated as the existing user.
-6.'Name' must contains 4 to 40 characters.
+4.'Password' must contain at least six characters, uppercase and lowercase letters, digits.
+5.'Username' must contain 2 to 20 characters and cannot be duplicated as the existing user.
+6.'Name' must contain 2 to 20 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
 8.'Expired Time' format should match yyyy-MM-dd.
 9.'Introduction' should less than 1000 character.</t>
@@ -54,10 +54,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -91,22 +91,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -120,13 +127,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
@@ -142,6 +142,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
@@ -149,9 +173,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,7 +182,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -172,8 +209,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -187,55 +225,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,49 +250,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -304,133 +406,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -448,16 +448,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -477,16 +483,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -527,165 +533,159 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Username</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>Role</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Student Number</t>
   </si>
   <si>
     <t>Expired Date</t>
@@ -52,7 +58,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -90,13 +96,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -112,10 +111,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,32 +158,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,6 +198,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -174,68 +227,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +256,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,163 +436,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,11 +450,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -468,21 +513,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -498,17 +528,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,169 +547,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -694,68 +700,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1024,20 +1030,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="20.2410714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5446428571429" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6785714285714" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6964285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.2416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.675" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.6428571428571" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="6" max="8" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.6416666666667" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1053,26 +1059,34 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="8"/>
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
   <si>
     <t>Note:
 1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 1000 pieces of data.
-2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).
+2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).If the entered organization or role is not found, it is necessary to modify it correctly before re-importing all the data.
 3.'Username', 'Name', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
 4.'Password' must contain at least six characters, uppercase and lowercase letters, digits.
 5.'Username' must contain 2 to 20 characters and cannot be duplicated as the existing user.
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -79,22 +79,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Arial Regular"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial Regular"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -112,10 +105,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,32 +152,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,6 +192,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -174,68 +221,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +250,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,163 +430,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,11 +444,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -468,21 +507,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -498,17 +522,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,169 +541,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -694,68 +694,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1025,19 +1025,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.2410714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5446428571429" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6785714285714" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6964285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.2416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.675" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.6428571428571" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.6416666666667" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1053,21 +1053,21 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="8"/>
     </row>
   </sheetData>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 3.'Username', 'Name', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
 4.'Password' must contain at least six characters, uppercase and lowercase letters, digits.
 5.'Username' must contain 2 to 20 characters and cannot be duplicated as the existing user.
-6.'Name' must contain 2 to 20 characters.
+6.'Name' must contain 4 to 40 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
 8.'Expired Time' format should match yyyy-MM-dd.
 9.'Introduction' should less than 1000 character.</t>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -79,22 +79,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Arial Regular"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial Regular"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -112,10 +105,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,32 +152,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,6 +192,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -174,68 +221,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,19 +250,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,163 +430,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,11 +444,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -468,21 +507,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -498,17 +522,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,169 +541,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -694,68 +694,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
-    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
-    <cellStyle name="输入" xfId="4" builtinId="20"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
-    <cellStyle name="货币" xfId="7" builtinId="4"/>
-    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
-    <cellStyle name="百分比" xfId="9" builtinId="5"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
-    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
-    <cellStyle name="计算" xfId="15" builtinId="22"/>
-    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
-    <cellStyle name="适中" xfId="17" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
-    <cellStyle name="好" xfId="19" builtinId="26"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
     <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="差" xfId="22" builtinId="27"/>
-    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
-    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
-    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
-    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
-    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
-    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
-    <cellStyle name="标题" xfId="33" builtinId="15"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
-    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
     <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="注释" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
-    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
-    <cellStyle name="超链接" xfId="41" builtinId="8"/>
-    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
-    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
-    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1025,19 +1025,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.2410714285714" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5446428571429" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6785714285714" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6964285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.2416666666667" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5416666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.675" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="18.6428571428571" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.6416666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.6416666666667" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1053,21 +1053,21 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="8"/>
     </row>
   </sheetData>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -19,7 +32,7 @@
     <t>Username</t>
   </si>
   <si>
-    <t>Name</t>
+    <t>Nickname</t>
   </si>
   <si>
     <t>Password</t>
@@ -52,7 +65,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>

--- a/mp-auth/src/main/resources/excel/import_template_en.xlsx
+++ b/mp-auth/src/main/resources/excel/import_template_en.xlsx
@@ -53,10 +53,10 @@
     <t>Note:
 1.Don't change the first two lines of the table or the name of the worksheet. Fill in user data from the third line and import a maximum of 1000 pieces of data.
 2.Enter the path of the organization in 'Organization path' field, for example, 'AA Company/Marketing/Sales Dept.'. Enter the role name in 'Role' field. Separate multiple role with commas (,).
-3.'Username', 'Name', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
+3.'Username', 'Nickname', 'Password' and 'Role' are mandatory. If 'Organization' not specified, the top 1 organization will be filled by default.
 4.'Password' must contain at least six characters, uppercase and lowercase letters, digits.
 5.'Username' must contain 2 to 20 characters and cannot be duplicated as the existing user.
-6.'Name' must contain 4 to 40 characters.
+6.'Nickname' must contain 4 to 40 characters.
 7.The cells' format is text. The first 100 lines of this file are text format. Changing the content will not affect the format of the content that has been filled.
 8.'Expired Time' format should match yyyy-MM-dd.
 9.'Introduction' should less than 1000 character.</t>
@@ -1073,7 +1073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" ht="213" customHeight="1" spans="1:6">
       <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
